--- a/03_Group_comparisons/Proteome/07_Cluster_Phenotype/c_data/cluster_phenotype.xlsx
+++ b/03_Group_comparisons/Proteome/07_Cluster_Phenotype/c_data/cluster_phenotype.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="212">
   <si>
     <t>sheet</t>
   </si>
@@ -240,16 +240,16 @@
     <t>clusters</t>
   </si>
   <si>
-    <t>03_Cluster_groups/Proteome/01_Clustering/c_data/clustering.xlsx</t>
-  </si>
-  <si>
-    <t>26ee0be84eef1dc9b7cd280844dda3e8</t>
+    <t>02_Groups/Proteome/c_data/clustering.xlsx</t>
+  </si>
+  <si>
+    <t>8e04a957cceabf91ead651b89d51dd35</t>
   </si>
   <si>
     <t>phenotype</t>
   </si>
   <si>
-    <t>00_Input/phenotype.csv</t>
+    <t>00_Setup/Input/phenotype.csv</t>
   </si>
   <si>
     <t>5a1989db406daa0b70189a9f0df52cf3</t>
@@ -357,12 +357,24 @@
     <t>1.2.1</t>
   </si>
   <si>
+    <t>evaluate</t>
+  </si>
+  <si>
+    <t>1.0.5</t>
+  </si>
+  <si>
     <t>farver</t>
   </si>
   <si>
     <t>2.1.2</t>
   </si>
   <si>
+    <t>fastmap</t>
+  </si>
+  <si>
+    <t>1.2.0</t>
+  </si>
+  <si>
     <t>foreach</t>
   </si>
   <si>
@@ -414,6 +426,18 @@
     <t>1.1.4</t>
   </si>
   <si>
+    <t>htmltools</t>
+  </si>
+  <si>
+    <t>0.5.9</t>
+  </si>
+  <si>
+    <t>htmlwidgets</t>
+  </si>
+  <si>
+    <t>1.6.4</t>
+  </si>
+  <si>
     <t>IRanges</t>
   </si>
   <si>
@@ -426,6 +450,18 @@
     <t>1.0.14</t>
   </si>
   <si>
+    <t>jsonlite</t>
+  </si>
+  <si>
+    <t>2.0.0</t>
+  </si>
+  <si>
+    <t>knitr</t>
+  </si>
+  <si>
+    <t>1.51</t>
+  </si>
+  <si>
     <t>labeling</t>
   </si>
   <si>
@@ -435,9 +471,6 @@
     <t>lifecycle</t>
   </si>
   <si>
-    <t>1.0.5</t>
-  </si>
-  <si>
     <t>magrittr</t>
   </si>
   <si>
@@ -450,6 +483,12 @@
     <t>1.5.0</t>
   </si>
   <si>
+    <t>otel</t>
+  </si>
+  <si>
+    <t>0.2.0</t>
+  </si>
+  <si>
     <t>pillar</t>
   </si>
   <si>
@@ -519,6 +558,12 @@
     <t>CRAN (R 4.6.1)</t>
   </si>
   <si>
+    <t>rmarkdown</t>
+  </si>
+  <si>
+    <t>2.31</t>
+  </si>
+  <si>
     <t>rprojroot</t>
   </si>
   <si>
@@ -576,6 +621,12 @@
     <t>0.5.0</t>
   </si>
   <si>
+    <t>utf8</t>
+  </si>
+  <si>
+    <t>1.2.6</t>
+  </si>
+  <si>
     <t>vctrs</t>
   </si>
   <si>
@@ -592,6 +643,18 @@
   </si>
   <si>
     <t>3.0.2</t>
+  </si>
+  <si>
+    <t>xfun</t>
+  </si>
+  <si>
+    <t>0.57</t>
+  </si>
+  <si>
+    <t>yaml</t>
+  </si>
+  <si>
+    <t>2.3.12</t>
   </si>
 </sst>
 </file>
@@ -4670,7 +4733,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:C68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
@@ -4920,7 +4983,7 @@
         <v>122</v>
       </c>
       <c r="B23" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="C23" t="s">
         <v>83</v>
@@ -4928,10 +4991,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B24" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C24" t="s">
         <v>83</v>
@@ -4939,10 +5002,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B25" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C25" t="s">
         <v>83</v>
@@ -4978,7 +5041,7 @@
         <v>132</v>
       </c>
       <c r="C28" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -5022,7 +5085,7 @@
         <v>140</v>
       </c>
       <c r="C32" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -5074,7 +5137,7 @@
         <v>149</v>
       </c>
       <c r="B37" t="s">
-        <v>150</v>
+        <v>113</v>
       </c>
       <c r="C37" t="s">
         <v>83</v>
@@ -5082,10 +5145,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
+        <v>150</v>
+      </c>
+      <c r="B38" t="s">
         <v>151</v>
-      </c>
-      <c r="B38" t="s">
-        <v>152</v>
       </c>
       <c r="C38" t="s">
         <v>83</v>
@@ -5093,10 +5156,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
+        <v>152</v>
+      </c>
+      <c r="B39" t="s">
         <v>153</v>
-      </c>
-      <c r="B39" t="s">
-        <v>154</v>
       </c>
       <c r="C39" t="s">
         <v>83</v>
@@ -5104,10 +5167,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
+        <v>154</v>
+      </c>
+      <c r="B40" t="s">
         <v>155</v>
-      </c>
-      <c r="B40" t="s">
-        <v>156</v>
       </c>
       <c r="C40" t="s">
         <v>83</v>
@@ -5115,10 +5178,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
+        <v>156</v>
+      </c>
+      <c r="B41" t="s">
         <v>157</v>
-      </c>
-      <c r="B41" t="s">
-        <v>158</v>
       </c>
       <c r="C41" t="s">
         <v>83</v>
@@ -5126,10 +5189,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
+        <v>158</v>
+      </c>
+      <c r="B42" t="s">
         <v>159</v>
-      </c>
-      <c r="B42" t="s">
-        <v>160</v>
       </c>
       <c r="C42" t="s">
         <v>83</v>
@@ -5137,10 +5200,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
+        <v>160</v>
+      </c>
+      <c r="B43" t="s">
         <v>161</v>
-      </c>
-      <c r="B43" t="s">
-        <v>162</v>
       </c>
       <c r="C43" t="s">
         <v>83</v>
@@ -5148,21 +5211,21 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
+        <v>162</v>
+      </c>
+      <c r="B44" t="s">
         <v>163</v>
       </c>
-      <c r="B44" t="s">
-        <v>164</v>
-      </c>
       <c r="C44" t="s">
-        <v>165</v>
+        <v>83</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B45" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C45" t="s">
         <v>83</v>
@@ -5170,21 +5233,21 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B46" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C46" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B47" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C47" t="s">
         <v>83</v>
@@ -5192,10 +5255,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B48" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C48" t="s">
         <v>83</v>
@@ -5203,10 +5266,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B49" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C49" t="s">
         <v>83</v>
@@ -5214,10 +5277,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B50" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C50" t="s">
         <v>83</v>
@@ -5225,21 +5288,21 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
+        <v>176</v>
+      </c>
+      <c r="B51" t="s">
+        <v>177</v>
+      </c>
+      <c r="C51" t="s">
         <v>178</v>
-      </c>
-      <c r="B51" t="s">
-        <v>179</v>
-      </c>
-      <c r="C51" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
+        <v>179</v>
+      </c>
+      <c r="B52" t="s">
         <v>180</v>
-      </c>
-      <c r="B52" t="s">
-        <v>181</v>
       </c>
       <c r="C52" t="s">
         <v>83</v>
@@ -5247,10 +5310,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
+        <v>181</v>
+      </c>
+      <c r="B53" t="s">
         <v>182</v>
-      </c>
-      <c r="B53" t="s">
-        <v>111</v>
       </c>
       <c r="C53" t="s">
         <v>83</v>
@@ -5264,7 +5327,7 @@
         <v>184</v>
       </c>
       <c r="C54" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -5297,6 +5360,127 @@
         <v>190</v>
       </c>
       <c r="C57" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" t="s">
+        <v>191</v>
+      </c>
+      <c r="B58" t="s">
+        <v>192</v>
+      </c>
+      <c r="C58" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" t="s">
+        <v>193</v>
+      </c>
+      <c r="B59" t="s">
+        <v>194</v>
+      </c>
+      <c r="C59" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" t="s">
+        <v>195</v>
+      </c>
+      <c r="B60" t="s">
+        <v>196</v>
+      </c>
+      <c r="C60" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" t="s">
+        <v>197</v>
+      </c>
+      <c r="B61" t="s">
+        <v>111</v>
+      </c>
+      <c r="C61" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" t="s">
+        <v>198</v>
+      </c>
+      <c r="B62" t="s">
+        <v>199</v>
+      </c>
+      <c r="C62" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" t="s">
+        <v>200</v>
+      </c>
+      <c r="B63" t="s">
+        <v>201</v>
+      </c>
+      <c r="C63" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" t="s">
+        <v>202</v>
+      </c>
+      <c r="B64" t="s">
+        <v>203</v>
+      </c>
+      <c r="C64" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" t="s">
+        <v>204</v>
+      </c>
+      <c r="B65" t="s">
+        <v>205</v>
+      </c>
+      <c r="C65" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" t="s">
+        <v>206</v>
+      </c>
+      <c r="B66" t="s">
+        <v>207</v>
+      </c>
+      <c r="C66" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" t="s">
+        <v>208</v>
+      </c>
+      <c r="B67" t="s">
+        <v>209</v>
+      </c>
+      <c r="C67" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" t="s">
+        <v>210</v>
+      </c>
+      <c r="B68" t="s">
+        <v>211</v>
+      </c>
+      <c r="C68" t="s">
         <v>83</v>
       </c>
     </row>

--- a/03_Group_comparisons/Proteome/07_Cluster_Phenotype/c_data/cluster_phenotype.xlsx
+++ b/03_Group_comparisons/Proteome/07_Cluster_Phenotype/c_data/cluster_phenotype.xlsx
@@ -243,7 +243,7 @@
     <t>02_Groups/Proteome/c_data/clustering.xlsx</t>
   </si>
   <si>
-    <t>8e04a957cceabf91ead651b89d51dd35</t>
+    <t>65506da788b47182e1478149f673bdfd</t>
   </si>
   <si>
     <t>phenotype</t>
